--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AALR3</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -593,7 +593,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -660,7 +660,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -727,7 +727,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -794,7 +794,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -861,7 +861,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -928,7 +928,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALLD3</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -995,7 +995,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1062,7 +1062,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1129,7 +1129,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALPK3</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1196,7 +1196,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1263,7 +1263,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALUP4</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AMAR3</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1397,7 +1397,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AMBP3</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1464,7 +1464,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AMER3</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1531,7 +1531,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AMOB3</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1598,7 +1598,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANIM3</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1665,7 +1665,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1732,7 +1732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASAI3</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1799,7 +1799,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ATED3</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1866,7 +1866,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AURA33</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1933,7 +1933,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2000,7 +2000,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AZEV4</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2067,7 +2067,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AZTE3</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2134,7 +2134,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2201,7 +2201,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>B3SA3</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2268,7 +2268,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAZA3</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2335,7 +2335,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2402,7 +2402,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2469,7 +2469,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2536,7 +2536,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2603,7 +2603,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2670,7 +2670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEES4</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2737,7 +2737,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BGIP4</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2804,7 +2804,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2871,7 +2871,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BIOM3</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2938,7 +2938,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BLAU3</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -3005,7 +3005,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BMEB4</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -3072,7 +3072,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BMGB4</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3139,7 +3139,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3206,7 +3206,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -3273,7 +3273,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRAP3</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -3340,7 +3340,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRAP4</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -3407,7 +3407,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRAV3</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3474,7 +3474,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRBI11</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3541,7 +3541,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRKM3</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3608,7 +3608,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3675,7 +3675,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3742,7 +3742,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BRST3</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3809,7 +3809,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BSLI4</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3876,7 +3876,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3943,7 +3943,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4010,7 +4010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CASH3</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -4077,7 +4077,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -4144,7 +4144,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -4211,7 +4211,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CGRA4</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -4278,7 +4278,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CLSC4</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -4345,7 +4345,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -4412,7 +4412,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -4479,7 +4479,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -4546,7 +4546,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -4613,7 +4613,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -4680,7 +4680,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -4747,7 +4747,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4814,7 +4814,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4881,7 +4881,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CSED3</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4948,7 +4948,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -5015,7 +5015,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -5082,7 +5082,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -5149,7 +5149,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -5216,7 +5216,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -5283,7 +5283,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -5350,7 +5350,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -5417,7 +5417,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -5484,7 +5484,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DEXP3</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -5551,7 +5551,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DEXP4</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -5618,7 +5618,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -5685,7 +5685,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -5752,7 +5752,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DOTZ3</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -5819,7 +5819,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -5886,7 +5886,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EALT4</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -5953,7 +5953,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -6020,7 +6020,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -6087,7 +6087,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EMAE4</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -6154,7 +6154,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -6221,7 +6221,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -6288,7 +6288,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ENGI3</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -6355,7 +6355,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ENJU3</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -6422,7 +6422,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EQPA3</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -6489,7 +6489,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -6556,7 +6556,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ESPA3</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -6623,7 +6623,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EUCA3</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -6690,7 +6690,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EUCA4</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -6757,7 +6757,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -6824,7 +6824,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -6891,7 +6891,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -6958,7 +6958,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FHER3</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -7025,7 +7025,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FICT3</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -7092,7 +7092,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FIQE3</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -7159,7 +7159,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -7226,7 +7226,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FRAS3</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -7293,7 +7293,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>G2DI33</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -7360,7 +7360,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -7427,7 +7427,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GGBR3</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -7494,7 +7494,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -7561,7 +7561,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -7628,7 +7628,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -7695,7 +7695,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOAU3</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -7762,7 +7762,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -7829,7 +7829,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -7896,7 +7896,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -7963,7 +7963,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8030,7 +8030,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HBRE3</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -8097,7 +8097,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -8164,7 +8164,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -8231,7 +8231,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IFCM3</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8298,7 +8298,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -8365,7 +8365,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -8432,7 +8432,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -8499,7 +8499,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IRBR3</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -8566,7 +8566,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ISAE4</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -8633,7 +8633,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -8700,7 +8700,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -8767,7 +8767,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -8834,7 +8834,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -8901,7 +8901,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -8968,7 +8968,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KEPL3</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -9035,7 +9035,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -9102,7 +9102,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -9169,7 +9169,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LAND3</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -9236,7 +9236,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -9303,7 +9303,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -9370,7 +9370,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -9437,7 +9437,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LJQQ3</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -9504,7 +9504,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LOGG3</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -9571,7 +9571,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -9638,7 +9638,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LPSB3</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -9705,7 +9705,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -9772,7 +9772,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LUPA3</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -9839,7 +9839,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LWSA3</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -9906,7 +9906,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MATD3</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -9973,7 +9973,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MBRF3</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -10040,7 +10040,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -10107,7 +10107,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -10174,7 +10174,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MEAL3</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -10241,7 +10241,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -10308,7 +10308,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -10375,7 +10375,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MILS3</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -10442,7 +10442,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MLAS3</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -10509,7 +10509,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOTV3</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -10576,7 +10576,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -10643,7 +10643,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -10710,7 +10710,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTRE3</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -10777,7 +10777,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -10844,7 +10844,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -10911,7 +10911,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NATU3</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -10978,7 +10978,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -11045,7 +11045,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NGRD3</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -11112,7 +11112,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -11179,7 +11179,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OFSA3</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -11246,7 +11246,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -11313,7 +11313,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -11380,7 +11380,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OPCT3</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -11447,7 +11447,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ORVR3</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -11514,7 +11514,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -11581,7 +11581,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PDGR3</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -11648,7 +11648,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PDTC3</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -11715,7 +11715,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -11782,7 +11782,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -11849,7 +11849,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PFRM3</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -11916,7 +11916,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -11983,7 +11983,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -12050,7 +12050,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -12117,7 +12117,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PMAM3</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -12184,7 +12184,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -12251,7 +12251,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>POMO3</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -12318,7 +12318,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -12385,7 +12385,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>POSI3</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -12452,7 +12452,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -12519,7 +12519,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PRNR3</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -12586,7 +12586,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -12653,7 +12653,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -12720,7 +12720,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PTNT4</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -12787,7 +12787,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -12854,7 +12854,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -12921,7 +12921,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -12988,7 +12988,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -13055,7 +13055,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANI3</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -13122,7 +13122,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAPT3</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -13189,7 +13189,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -13256,7 +13256,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RCSL4</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -13323,7 +13323,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -13390,7 +13390,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -13457,7 +13457,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -13524,7 +13524,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -13591,7 +13591,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -13658,7 +13658,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -13725,7 +13725,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAPR4</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -13792,7 +13792,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -13859,7 +13859,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -13926,7 +13926,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -13993,7 +13993,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -14060,7 +14060,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -14127,7 +14127,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHOW3</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -14194,7 +14194,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHUL4</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -14261,7 +14261,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -14328,7 +14328,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -14395,7 +14395,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -14462,7 +14462,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -14529,7 +14529,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -14596,7 +14596,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -14663,7 +14663,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -14730,7 +14730,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -14797,7 +14797,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TAEE4</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -14864,7 +14864,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TCSA3</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -14931,7 +14931,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TECN3</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -14998,7 +14998,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TEND3</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -15065,7 +15065,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -15132,7 +15132,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -15199,7 +15199,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -15266,7 +15266,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -15333,7 +15333,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TPIS3</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -15400,7 +15400,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TRAD3</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -15467,7 +15467,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TRIS3</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -15534,7 +15534,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -15601,7 +15601,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -15668,7 +15668,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UCAS3</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -15735,7 +15735,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -15802,7 +15802,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -15869,7 +15869,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -15936,7 +15936,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -16003,7 +16003,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -16070,7 +16070,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -16137,7 +16137,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -16204,7 +16204,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VITT3</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -16271,7 +16271,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -16338,7 +16338,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIVR3</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -16405,7 +16405,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -16472,7 +16472,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -16539,7 +16539,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VSTE3</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -16606,7 +16606,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VTRU3</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -16673,7 +16673,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -16740,7 +16740,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VVEO3</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -16807,7 +16807,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -16874,7 +16874,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>WEST3</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -16941,7 +16941,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>WIZC3</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -17008,7 +17008,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B248" t="n">
